--- a/dist/templates/CLRA_Act_1970/Form_XXIII_Register_of_Overtime.xlsx
+++ b/dist/templates/CLRA_Act_1970/Form_XXIII_Register_of_Overtime.xlsx
@@ -292,7 +292,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -329,6 +329,13 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
         <color rgb="FFA0A0A0"/>
@@ -374,72 +381,76 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -698,727 +709,727 @@
   <dimension ref="A1:N39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="38.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="38.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="7"/>
+      <c r="H4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="10" t="s">
+      <c r="G5" s="10"/>
+      <c r="H5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="N7" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16"/>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="12">
